--- a/data/availability/projects/palm-hills-developments/hacienda-heneish.xlsx
+++ b/data/availability/projects/palm-hills-developments/hacienda-heneish.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Template for Hacienda Heneish</t>
+          <t>Live inventory for hacienda-heneish</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,106 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hacienda-heneish</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>196</v>
+      </c>
+      <c r="F2" t="n">
+        <v>196</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>HH-Phase 1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2028-06-30</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hacienda-heneish</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>145</v>
+      </c>
+      <c r="F3" t="n">
+        <v>145</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="H3" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>HH-Phase 2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2029-06-30</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
         </is>
       </c>
     </row>
@@ -557,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +724,120 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hacienda-heneish</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HH-TH2-704-05</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HH-Phase 1</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>196</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>38213000</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2028-06-30</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hacienda-heneish</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HH-BL7-1013-11</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HH-Phase 2</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>145</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>22110000</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2029-06-30</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>

--- a/data/availability/projects/palm-hills-developments/hacienda-heneish.xlsx
+++ b/data/availability/projects/palm-hills-developments/hacienda-heneish.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -859,7 +859,6 @@
       <c r="G2" t="n">
         <v>67.5</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -870,7 +869,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -916,7 +915,6 @@
       <c r="G3" t="n">
         <v>155.5</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -927,7 +925,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -973,7 +971,6 @@
       <c r="G4" t="n">
         <v>114.5</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -984,7 +981,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1030,7 +1027,6 @@
       <c r="G5" t="n">
         <v>114.5</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1041,7 +1037,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1087,7 +1083,6 @@
       <c r="G6" t="n">
         <v>253</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1098,7 +1093,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
